--- a/www/download/COUNTRY.CHN.WIOD16.xlsx
+++ b/www/download/COUNTRY.CHN.WIOD16.xlsx
@@ -342,7 +342,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:AC37"/>
+  <dimension ref="A1:AC55"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -500,7 +500,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>China</t>
         </is>
       </c>
     </row>
@@ -510,6 +510,11 @@
           <t>Computation method</t>
         </is>
       </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>Standard v0.9</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -847,1848 +852,3409 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Capital depreciation (USD)</t>
+          <t>Exchange rate (USD)</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>capital_depreciation.s.us</t>
+          <t>exchange.r.us</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>0.265</t>
+          <t>8.27855690333697</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>0.291</t>
+          <t>8.27691240338643</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>0.322</t>
+          <t>8.27704939102898</t>
         </is>
       </c>
       <c r="K9" t="inlineStr">
         <is>
-          <t>0.386</t>
+          <t>8.27698087962518</t>
         </is>
       </c>
       <c r="L9" t="inlineStr">
         <is>
-          <t>0.476</t>
+          <t>8.27691237067746</t>
         </is>
       </c>
       <c r="M9" t="inlineStr">
         <is>
-          <t>0.575</t>
+          <t>8.19336337514046</t>
         </is>
       </c>
       <c r="N9" t="inlineStr">
         <is>
-          <t>0.666</t>
+          <t>7.97270138586024</t>
         </is>
       </c>
       <c r="O9" t="inlineStr">
         <is>
-          <t>0.776</t>
+          <t>7.60531450957138</t>
         </is>
       </c>
       <c r="P9" t="inlineStr">
         <is>
-          <t>1.063</t>
+          <t>6.94589150908069</t>
         </is>
       </c>
       <c r="Q9" t="inlineStr">
         <is>
-          <t>1.221</t>
+          <t>6.83139434388019</t>
         </is>
       </c>
       <c r="R9" t="inlineStr">
         <is>
-          <t>1.487</t>
+          <t>6.76956399844481</t>
         </is>
       </c>
       <c r="S9" t="inlineStr">
         <is>
-          <t>1.883</t>
+          <t>6.46011522202256</t>
         </is>
       </c>
       <c r="T9" t="inlineStr">
         <is>
-          <t>2.225</t>
+          <t>6.31229445096852</t>
         </is>
       </c>
       <c r="U9" t="inlineStr">
         <is>
-          <t>2.549</t>
+          <t>6.19524946611821</t>
         </is>
       </c>
       <c r="V9" t="inlineStr">
         <is>
-          <t>2.847</t>
+          <t>6.14337404053866</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Number of employee</t>
+          <t>Rate of surplus value of high-skilled employee</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>emp.s.un</t>
-        </is>
-      </c>
-      <c r="H10" t="inlineStr">
-        <is>
-          <t>719.604</t>
-        </is>
-      </c>
-      <c r="I10" t="inlineStr">
-        <is>
-          <t>728.107</t>
-        </is>
-      </c>
-      <c r="J10" t="inlineStr">
-        <is>
-          <t>737.284</t>
-        </is>
-      </c>
-      <c r="K10" t="inlineStr">
-        <is>
-          <t>744.531</t>
-        </is>
-      </c>
-      <c r="L10" t="inlineStr">
-        <is>
-          <t>752.281</t>
-        </is>
-      </c>
-      <c r="M10" t="inlineStr">
-        <is>
-          <t>759.77</t>
-        </is>
-      </c>
-      <c r="N10" t="inlineStr">
-        <is>
-          <t>765.353</t>
-        </is>
-      </c>
-      <c r="O10" t="inlineStr">
-        <is>
-          <t>770.887</t>
-        </is>
-      </c>
-      <c r="P10" t="inlineStr">
-        <is>
-          <t>777.013</t>
-        </is>
-      </c>
-      <c r="Q10" t="inlineStr">
-        <is>
-          <t>784.924</t>
-        </is>
-      </c>
-      <c r="R10" t="inlineStr">
-        <is>
-          <t>784.663</t>
-        </is>
-      </c>
-      <c r="S10" t="inlineStr">
-        <is>
-          <t>840.443</t>
-        </is>
-      </c>
-      <c r="T10" t="inlineStr">
-        <is>
-          <t>854.216</t>
-        </is>
-      </c>
-      <c r="U10" t="inlineStr">
-        <is>
-          <t>857.826</t>
-        </is>
-      </c>
-      <c r="V10" t="inlineStr">
-        <is>
-          <t>858.367</t>
+          <t>surplus_value.empe_hs.r.pc</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Number of persons engaged</t>
+          <t>Rate of surplus value of medium-skilled employee</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>empe.s.un</t>
-        </is>
-      </c>
-      <c r="H11" t="inlineStr">
-        <is>
-          <t>271.888</t>
-        </is>
-      </c>
-      <c r="I11" t="inlineStr">
-        <is>
-          <t>281.049</t>
-        </is>
-      </c>
-      <c r="J11" t="inlineStr">
-        <is>
-          <t>290.755</t>
-        </is>
-      </c>
-      <c r="K11" t="inlineStr">
-        <is>
-          <t>299.897</t>
-        </is>
-      </c>
-      <c r="L11" t="inlineStr">
-        <is>
-          <t>309.413</t>
-        </is>
-      </c>
-      <c r="M11" t="inlineStr">
-        <is>
-          <t>318.997</t>
-        </is>
-      </c>
-      <c r="N11" t="inlineStr">
-        <is>
-          <t>327.893</t>
-        </is>
-      </c>
-      <c r="O11" t="inlineStr">
-        <is>
-          <t>336.87</t>
-        </is>
-      </c>
-      <c r="P11" t="inlineStr">
-        <is>
-          <t>346.221</t>
-        </is>
-      </c>
-      <c r="Q11" t="inlineStr">
-        <is>
-          <t>356.505</t>
-        </is>
-      </c>
-      <c r="R11" t="inlineStr">
-        <is>
-          <t>363.142</t>
-        </is>
-      </c>
-      <c r="S11" t="inlineStr">
-        <is>
-          <t>396.126</t>
-        </is>
-      </c>
-      <c r="T11" t="inlineStr">
-        <is>
-          <t>409.87</t>
-        </is>
-      </c>
-      <c r="U11" t="inlineStr">
-        <is>
-          <t>418.859</t>
-        </is>
-      </c>
-      <c r="V11" t="inlineStr">
-        <is>
-          <t>426.36</t>
+          <t>surplus_value.empe_ms.r.pc</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Total hours worked by persons engaged</t>
+          <t>Rate of surplus value of low-skilled employee</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>hours_worked.emp.s.hr</t>
-        </is>
-      </c>
-      <c r="H12" t="inlineStr">
-        <is>
-          <t>1281154.752</t>
-        </is>
-      </c>
-      <c r="I12" t="inlineStr">
-        <is>
-          <t>1358661.991</t>
-        </is>
-      </c>
-      <c r="J12" t="inlineStr">
-        <is>
-          <t>1430092.97</t>
-        </is>
-      </c>
-      <c r="K12" t="inlineStr">
-        <is>
-          <t>1472458.079</t>
-        </is>
-      </c>
-      <c r="L12" t="inlineStr">
-        <is>
-          <t>1501021.793</t>
-        </is>
-      </c>
-      <c r="M12" t="inlineStr">
-        <is>
-          <t>1509876.006</t>
-        </is>
-      </c>
-      <c r="N12" t="inlineStr">
-        <is>
-          <t>1494135.694</t>
-        </is>
-      </c>
-      <c r="O12" t="inlineStr">
-        <is>
-          <t>1519893.748</t>
-        </is>
-      </c>
-      <c r="P12" t="inlineStr">
-        <is>
-          <t>1568479.449</t>
-        </is>
-      </c>
-      <c r="Q12" t="inlineStr">
-        <is>
-          <t>1591354.705</t>
-        </is>
-      </c>
-      <c r="R12" t="inlineStr">
-        <is>
-          <t>1597046.567</t>
-        </is>
-      </c>
-      <c r="S12" t="inlineStr">
-        <is>
-          <t>1736502.387</t>
-        </is>
-      </c>
-      <c r="T12" t="inlineStr">
-        <is>
-          <t>1770099.919</t>
-        </is>
-      </c>
-      <c r="U12" t="inlineStr">
-        <is>
-          <t>1784985.375</t>
-        </is>
-      </c>
-      <c r="V12" t="inlineStr">
-        <is>
-          <t>1790192.448</t>
+          <t>surplus_value.empe_ls.r.pc</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Total hours worked by employees</t>
+          <t>Gross output (magnitude of value)</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>hours_worked.empe.s.hr</t>
+          <t>gross_output.s.mv</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>484058.712</t>
+          <t>2070988312458.52</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>524443.508</t>
+          <t>2027541731647.35</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>563971.475</t>
+          <t>2027720231538.24</t>
         </is>
       </c>
       <c r="K13" t="inlineStr">
         <is>
-          <t>593106.096</t>
+          <t>2075914706027.34</t>
         </is>
       </c>
       <c r="L13" t="inlineStr">
         <is>
-          <t>617370.28</t>
+          <t>2151404318607.03</t>
         </is>
       </c>
       <c r="M13" t="inlineStr">
         <is>
-          <t>633936.541</t>
+          <t>2256372916884.74</t>
         </is>
       </c>
       <c r="N13" t="inlineStr">
         <is>
-          <t>640117.6</t>
+          <t>2428032198361.37</t>
         </is>
       </c>
       <c r="O13" t="inlineStr">
         <is>
-          <t>664178.389</t>
+          <t>2527008145327.51</t>
         </is>
       </c>
       <c r="P13" t="inlineStr">
         <is>
-          <t>698883.052</t>
+          <t>2685415720816.95</t>
         </is>
       </c>
       <c r="Q13" t="inlineStr">
         <is>
-          <t>722777.373</t>
+          <t>2852235648027.67</t>
         </is>
       </c>
       <c r="R13" t="inlineStr">
         <is>
-          <t>739113.132</t>
+          <t>2809638482886.83</t>
         </is>
       </c>
       <c r="S13" t="inlineStr">
         <is>
-          <t>818465.66</t>
+          <t>3121502793210.12</t>
         </is>
       </c>
       <c r="T13" t="inlineStr">
         <is>
-          <t>849329.316</t>
+          <t>3236183854790.26</t>
         </is>
       </c>
       <c r="U13" t="inlineStr">
         <is>
-          <t>871572.643</t>
+          <t>3283099622808.27</t>
         </is>
       </c>
       <c r="V13" t="inlineStr">
         <is>
-          <t>889206.516</t>
+          <t>3226995572700.66</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Share of high-skilled labour compensation</t>
+          <t>Total labour force value (magnitude of value)</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>compensation.empe_hs.r.pc</t>
+          <t>labour_force_value.s.mv</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>502601689259.991</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>509122121759.879</t>
+        </is>
+      </c>
+      <c r="J14" t="inlineStr">
+        <is>
+          <t>527032802402.347</t>
+        </is>
+      </c>
+      <c r="K14" t="inlineStr">
+        <is>
+          <t>510049273702.906</t>
+        </is>
+      </c>
+      <c r="L14" t="inlineStr">
+        <is>
+          <t>508726957492.146</t>
+        </is>
+      </c>
+      <c r="M14" t="inlineStr">
+        <is>
+          <t>490154959977.541</t>
+        </is>
+      </c>
+      <c r="N14" t="inlineStr">
+        <is>
+          <t>499644326274.245</t>
+        </is>
+      </c>
+      <c r="O14" t="inlineStr">
+        <is>
+          <t>484642956847.919</t>
+        </is>
+      </c>
+      <c r="P14" t="inlineStr">
+        <is>
+          <t>534315891329.701</t>
+        </is>
+      </c>
+      <c r="Q14" t="inlineStr">
+        <is>
+          <t>570906186436.344</t>
+        </is>
+      </c>
+      <c r="R14" t="inlineStr">
+        <is>
+          <t>568953098882.618</t>
+        </is>
+      </c>
+      <c r="S14" t="inlineStr">
+        <is>
+          <t>603569017220.243</t>
+        </is>
+      </c>
+      <c r="T14" t="inlineStr">
+        <is>
+          <t>640737450899.619</t>
+        </is>
+      </c>
+      <c r="U14" t="inlineStr">
+        <is>
+          <t>623560014684.789</t>
+        </is>
+      </c>
+      <c r="V14" t="inlineStr">
+        <is>
+          <t>625720457189.654</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Share of medium-skilled labour compensation</t>
+          <t>Value per output</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>compensation.empe_ms.r.pc</t>
+          <t>value.m.mv</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>23019642.1687554</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>20840095.469653</t>
+        </is>
+      </c>
+      <c r="J15" t="inlineStr">
+        <is>
+          <t>19458447.6916964</t>
+        </is>
+      </c>
+      <c r="K15" t="inlineStr">
+        <is>
+          <t>17710069.596955</t>
+        </is>
+      </c>
+      <c r="L15" t="inlineStr">
+        <is>
+          <t>15319463.8549445</t>
+        </is>
+      </c>
+      <c r="M15" t="inlineStr">
+        <is>
+          <t>13355991.5426349</t>
+        </is>
+      </c>
+      <c r="N15" t="inlineStr">
+        <is>
+          <t>11893524.4210369</t>
+        </is>
+      </c>
+      <c r="O15" t="inlineStr">
+        <is>
+          <t>9476251.54122486</t>
+        </is>
+      </c>
+      <c r="P15" t="inlineStr">
+        <is>
+          <t>7912464.81795703</t>
+        </is>
+      </c>
+      <c r="Q15" t="inlineStr">
+        <is>
+          <t>7601135.83725244</t>
+        </is>
+      </c>
+      <c r="R15" t="inlineStr">
+        <is>
+          <t>6412307.19458914</t>
+        </is>
+      </c>
+      <c r="S15" t="inlineStr">
+        <is>
+          <t>5639907.10030699</t>
+        </is>
+      </c>
+      <c r="T15" t="inlineStr">
+        <is>
+          <t>5122193.19188271</t>
+        </is>
+      </c>
+      <c r="U15" t="inlineStr">
+        <is>
+          <t>4546168.53836047</t>
+        </is>
+      </c>
+      <c r="V15" t="inlineStr">
+        <is>
+          <t>4153601.58186137</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Share of low-skilled labour compensation</t>
+          <t>Gross Domestic Product (direct prices - USD)</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>compensation.empe_ls.r.pc</t>
+          <t>gdp.s.du</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>8083617.22303388</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>8029299.30783722</t>
+        </is>
+      </c>
+      <c r="J16" t="inlineStr">
+        <is>
+          <t>8210660.86618096</t>
+        </is>
+      </c>
+      <c r="K16" t="inlineStr">
+        <is>
+          <t>8804209.10681044</t>
+        </is>
+      </c>
+      <c r="L16" t="inlineStr">
+        <is>
+          <t>9754538.54177619</t>
+        </is>
+      </c>
+      <c r="M16" t="inlineStr">
+        <is>
+          <t>10460168.129824</t>
+        </is>
+      </c>
+      <c r="N16" t="inlineStr">
+        <is>
+          <t>11457552.6941972</t>
+        </is>
+      </c>
+      <c r="O16" t="inlineStr">
+        <is>
+          <t>13215370.9033115</t>
+        </is>
+      </c>
+      <c r="P16" t="inlineStr">
+        <is>
+          <t>14861899.1241105</t>
+        </is>
+      </c>
+      <c r="Q16" t="inlineStr">
+        <is>
+          <t>13669606.2868205</t>
+        </is>
+      </c>
+      <c r="R16" t="inlineStr">
+        <is>
+          <t>15105019.7029488</t>
+        </is>
+      </c>
+      <c r="S16" t="inlineStr">
+        <is>
+          <t>17404629.3221423</t>
+        </is>
+      </c>
+      <c r="T16" t="inlineStr">
+        <is>
+          <t>17057480.0132433</t>
+        </is>
+      </c>
+      <c r="U16" t="inlineStr">
+        <is>
+          <t>16835028.5110119</t>
+        </is>
+      </c>
+      <c r="V16" t="inlineStr">
+        <is>
+          <t>16584696.9405335</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Share of hours worked by high-skilled persons engaged</t>
+          <t>Gross output (direct prices - USD)</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>hours_worked.empe_hs.r.pc</t>
+          <t>gross_output.s.du</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>16827538.3632182</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr">
+        <is>
+          <t>16319670.6326982</t>
+        </is>
+      </c>
+      <c r="J17" t="inlineStr">
+        <is>
+          <t>16419066.7397775</t>
+        </is>
+      </c>
+      <c r="K17" t="inlineStr">
+        <is>
+          <t>18293520.2174473</t>
+        </is>
+      </c>
+      <c r="L17" t="inlineStr">
+        <is>
+          <t>20960410.7594234</t>
+        </is>
+      </c>
+      <c r="M17" t="inlineStr">
+        <is>
+          <t>23602746.1228143</t>
+        </is>
+      </c>
+      <c r="N17" t="inlineStr">
+        <is>
+          <t>26831736.8935333</t>
+        </is>
+      </c>
+      <c r="O17" t="inlineStr">
+        <is>
+          <t>31529721.1311535</t>
+        </is>
+      </c>
+      <c r="P17" t="inlineStr">
+        <is>
+          <t>36367619.5427881</t>
+        </is>
+      </c>
+      <c r="Q17" t="inlineStr">
+        <is>
+          <t>35151736.4033352</t>
+        </is>
+      </c>
+      <c r="R17" t="inlineStr">
+        <is>
+          <t>38362359.0872924</t>
+        </is>
+      </c>
+      <c r="S17" t="inlineStr">
+        <is>
+          <t>45261550.3586182</t>
+        </is>
+      </c>
+      <c r="T17" t="inlineStr">
+        <is>
+          <t>45720808.2372245</t>
+        </is>
+      </c>
+      <c r="U17" t="inlineStr">
+        <is>
+          <t>46337531.3974834</t>
+        </is>
+      </c>
+      <c r="V17" t="inlineStr">
+        <is>
+          <t>45756665.2508413</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Share of hours worked by medium-skilled persons engaged</t>
+          <t>Rate of surplus value</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>hours_worked.empe_ms.r.pc</t>
+          <t>surplus_value.empe.r.pc</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>-0.0368939807789499</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr">
+        <is>
+          <t>0.0300937342247858</t>
+        </is>
+      </c>
+      <c r="J18" t="inlineStr">
+        <is>
+          <t>0.0700879959034557</t>
+        </is>
+      </c>
+      <c r="K18" t="inlineStr">
+        <is>
+          <t>0.162840781554543</t>
+        </is>
+      </c>
+      <c r="L18" t="inlineStr">
+        <is>
+          <t>0.213559200069142</t>
+        </is>
+      </c>
+      <c r="M18" t="inlineStr">
+        <is>
+          <t>0.293339030298541</t>
+        </is>
+      </c>
+      <c r="N18" t="inlineStr">
+        <is>
+          <t>0.281146539832267</t>
+        </is>
+      </c>
+      <c r="O18" t="inlineStr">
+        <is>
+          <t>0.370448862308038</t>
+        </is>
+      </c>
+      <c r="P18" t="inlineStr">
+        <is>
+          <t>0.307996005920808</t>
+        </is>
+      </c>
+      <c r="Q18" t="inlineStr">
+        <is>
+          <t>0.266017762842506</t>
+        </is>
+      </c>
+      <c r="R18" t="inlineStr">
+        <is>
+          <t>0.299075675978803</t>
+        </is>
+      </c>
+      <c r="S18" t="inlineStr">
+        <is>
+          <t>0.356043197712259</t>
+        </is>
+      </c>
+      <c r="T18" t="inlineStr">
+        <is>
+          <t>0.325549668660983</t>
+        </is>
+      </c>
+      <c r="U18" t="inlineStr">
+        <is>
+          <t>0.397736580810075</t>
+        </is>
+      </c>
+      <c r="V18" t="inlineStr">
+        <is>
+          <t>0.42109228831731</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Share of hours worked by low-skilled persons engaged</t>
+          <t>Capital depreciation (USD)</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>hours_worked.empe_ls.r.pc</t>
+          <t>capital_depreciation.s.us</t>
+        </is>
+      </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>264950.425310826</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr">
+        <is>
+          <t>290188.679716937</t>
+        </is>
+      </c>
+      <c r="J19" t="inlineStr">
+        <is>
+          <t>321703.083679771</t>
+        </is>
+      </c>
+      <c r="K19" t="inlineStr">
+        <is>
+          <t>385509.978489976</t>
+        </is>
+      </c>
+      <c r="L19" t="inlineStr">
+        <is>
+          <t>475640.452410863</t>
+        </is>
+      </c>
+      <c r="M19" t="inlineStr">
+        <is>
+          <t>574629.586415355</t>
+        </is>
+      </c>
+      <c r="N19" t="inlineStr">
+        <is>
+          <t>664895.750370545</t>
+        </is>
+      </c>
+      <c r="O19" t="inlineStr">
+        <is>
+          <t>773668.164135119</t>
+        </is>
+      </c>
+      <c r="P19" t="inlineStr">
+        <is>
+          <t>1061895.41132444</t>
+        </is>
+      </c>
+      <c r="Q19" t="inlineStr">
+        <is>
+          <t>1220596.43264076</t>
+        </is>
+      </c>
+      <c r="R19" t="inlineStr">
+        <is>
+          <t>1485277.04892492</t>
+        </is>
+      </c>
+      <c r="S19" t="inlineStr">
+        <is>
+          <t>1881714.61776087</t>
+        </is>
+      </c>
+      <c r="T19" t="inlineStr">
+        <is>
+          <t>2222783.29465165</t>
+        </is>
+      </c>
+      <c r="U19" t="inlineStr">
+        <is>
+          <t>2550462.83095725</t>
+        </is>
+      </c>
+      <c r="V19" t="inlineStr">
+        <is>
+          <t>2848717.49668251</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Exchange rate (USD)</t>
+          <t>Labour force value (magnitude of value)</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>exchange.r.us</t>
+          <t>labour_force_value.m.mv</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>8.27855690333697</t>
+          <t>1848.56079318397</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>8.27691240338643</t>
+          <t>1811.50360759469</t>
         </is>
       </c>
       <c r="J20" t="inlineStr">
         <is>
-          <t>8.27704939102898</t>
+          <t>1812.63448798329</t>
         </is>
       </c>
       <c r="K20" t="inlineStr">
         <is>
-          <t>8.27698087962518</t>
+          <t>1700.74760283703</t>
         </is>
       </c>
       <c r="L20" t="inlineStr">
         <is>
-          <t>8.27691237067746</t>
+          <t>1644.16708707293</t>
         </is>
       </c>
       <c r="M20" t="inlineStr">
         <is>
-          <t>8.19336337514046</t>
+          <t>1536.55081229667</t>
         </is>
       </c>
       <c r="N20" t="inlineStr">
         <is>
-          <t>7.97270138586024</t>
+          <t>1523.8047922798</t>
         </is>
       </c>
       <c r="O20" t="inlineStr">
         <is>
-          <t>7.60531450957138</t>
+          <t>1438.66468640454</t>
         </is>
       </c>
       <c r="P20" t="inlineStr">
         <is>
-          <t>6.94589150908069</t>
+          <t>1543.27778715496</t>
         </is>
       </c>
       <c r="Q20" t="inlineStr">
         <is>
-          <t>6.83139434388019</t>
+          <t>1601.39924240303</t>
         </is>
       </c>
       <c r="R20" t="inlineStr">
         <is>
-          <t>6.76956399844481</t>
+          <t>1566.75182268602</t>
         </is>
       </c>
       <c r="S20" t="inlineStr">
         <is>
-          <t>6.46011522202256</t>
+          <t>1523.67936161835</t>
         </is>
       </c>
       <c r="T20" t="inlineStr">
         <is>
-          <t>6.31229445096852</t>
+          <t>1563.26977704461</t>
         </is>
       </c>
       <c r="U20" t="inlineStr">
         <is>
-          <t>6.19524946611821</t>
+          <t>1488.71082617799</t>
         </is>
       </c>
       <c r="V20" t="inlineStr">
         <is>
-          <t>6.14337404053866</t>
+          <t>1467.58832462613</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Compensation of employees (USD)</t>
+          <t>Value transfer through trade</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>compensation.empe.s.us</t>
+          <t>trade_transfers.s.mv</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>0.589</t>
+          <t>-90732877764.526</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>0.649</t>
+          <t>-85180821972.0065</t>
         </is>
       </c>
       <c r="J21" t="inlineStr">
         <is>
-          <t>0.709</t>
+          <t>-94328639701.5673</t>
         </is>
       </c>
       <c r="K21" t="inlineStr">
         <is>
-          <t>0.787</t>
+          <t>-113422574831.959</t>
         </is>
       </c>
       <c r="L21" t="inlineStr">
         <is>
-          <t>0.924</t>
+          <t>-133680036415.426</t>
         </is>
       </c>
       <c r="M21" t="inlineStr">
         <is>
-          <t>1.06</t>
+          <t>-154468314844.067</t>
         </is>
       </c>
       <c r="N21" t="inlineStr">
         <is>
-          <t>1.251</t>
+          <t>-163470029133.622</t>
         </is>
       </c>
       <c r="O21" t="inlineStr">
         <is>
-          <t>1.588</t>
+          <t>-162598656386.029</t>
         </is>
       </c>
       <c r="P21" t="inlineStr">
         <is>
-          <t>2.158</t>
+          <t>-145413080743.454</t>
         </is>
       </c>
       <c r="Q21" t="inlineStr">
         <is>
-          <t>2.479</t>
+          <t>-113719423590.278</t>
         </is>
       </c>
       <c r="R21" t="inlineStr">
         <is>
-          <t>3.036</t>
+          <t>-111009078144.768</t>
         </is>
       </c>
       <c r="S21" t="inlineStr">
         <is>
-          <t>3.897</t>
+          <t>-109001874533.974</t>
         </is>
       </c>
       <c r="T21" t="inlineStr">
         <is>
-          <t>4.577</t>
+          <t>-87760210323.5969</t>
         </is>
       </c>
       <c r="U21" t="inlineStr">
         <is>
-          <t>5.159</t>
+          <t>-70020058252.4771</t>
         </is>
       </c>
       <c r="V21" t="inlineStr">
         <is>
-          <t>5.666</t>
+          <t>-43535602552.2031</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Labour compensation (USD)</t>
+          <t>Value transfer through trade of productive sectors</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>compensation.emp.s.us</t>
+          <t>trade_transfers.p.s.mv</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>0.589</t>
+          <t>-94194997772.9676</t>
         </is>
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>0.649</t>
+          <t>-89327052398.1791</t>
         </is>
       </c>
       <c r="J22" t="inlineStr">
         <is>
-          <t>0.709</t>
+          <t>-99380754264.1057</t>
         </is>
       </c>
       <c r="K22" t="inlineStr">
         <is>
-          <t>0.787</t>
+          <t>-118211562080.594</t>
         </is>
       </c>
       <c r="L22" t="inlineStr">
         <is>
-          <t>0.924</t>
+          <t>-138358872417.413</t>
         </is>
       </c>
       <c r="M22" t="inlineStr">
         <is>
-          <t>1.06</t>
+          <t>-159264755329.729</t>
         </is>
       </c>
       <c r="N22" t="inlineStr">
         <is>
-          <t>1.251</t>
+          <t>-168972442531.45</t>
         </is>
       </c>
       <c r="O22" t="inlineStr">
         <is>
-          <t>1.588</t>
+          <t>-168223898002.291</t>
         </is>
       </c>
       <c r="P22" t="inlineStr">
         <is>
-          <t>2.158</t>
+          <t>-152296624277.82</t>
         </is>
       </c>
       <c r="Q22" t="inlineStr">
         <is>
-          <t>2.479</t>
+          <t>-121663444479.326</t>
         </is>
       </c>
       <c r="R22" t="inlineStr">
         <is>
-          <t>3.036</t>
+          <t>-120348271216.863</t>
         </is>
       </c>
       <c r="S22" t="inlineStr">
         <is>
-          <t>3.897</t>
+          <t>-120543659055.312</t>
         </is>
       </c>
       <c r="T22" t="inlineStr">
         <is>
-          <t>4.577</t>
+          <t>-100294670108.783</t>
         </is>
       </c>
       <c r="U22" t="inlineStr">
         <is>
-          <t>5.159</t>
+          <t>-79283994005.2269</t>
         </is>
       </c>
       <c r="V22" t="inlineStr">
         <is>
-          <t>5.666</t>
+          <t>-52401154024.1778</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Capital stock (USD)</t>
+          <t>Value transfer through trade of unproductive sectors</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>capital_stock.s.us</t>
+          <t>trade_transfers.u.s.mv</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>2.994</t>
+          <t>3462120008.44167</t>
         </is>
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>3.358</t>
+          <t>4146230426.17262</t>
         </is>
       </c>
       <c r="J23" t="inlineStr">
         <is>
-          <t>3.788</t>
+          <t>5052114562.53832</t>
         </is>
       </c>
       <c r="K23" t="inlineStr">
         <is>
-          <t>4.422</t>
+          <t>4788987248.63546</t>
         </is>
       </c>
       <c r="L23" t="inlineStr">
         <is>
-          <t>5.326</t>
+          <t>4678836001.98723</t>
         </is>
       </c>
       <c r="M23" t="inlineStr">
         <is>
-          <t>6.376</t>
+          <t>4796440485.66203</t>
         </is>
       </c>
       <c r="N23" t="inlineStr">
         <is>
-          <t>7.636</t>
+          <t>5502413397.8275</t>
         </is>
       </c>
       <c r="O23" t="inlineStr">
         <is>
-          <t>9.346</t>
+          <t>5625241616.26126</t>
         </is>
       </c>
       <c r="P23" t="inlineStr">
         <is>
-          <t>12.592</t>
+          <t>6883543534.36623</t>
         </is>
       </c>
       <c r="Q23" t="inlineStr">
         <is>
-          <t>14.292</t>
+          <t>7944020889.04801</t>
         </is>
       </c>
       <c r="R23" t="inlineStr">
         <is>
-          <t>17.111</t>
+          <t>9339193072.09465</t>
         </is>
       </c>
       <c r="S23" t="inlineStr">
         <is>
-          <t>21.877</t>
+          <t>11541784521.3381</t>
         </is>
       </c>
       <c r="T23" t="inlineStr">
         <is>
-          <t>25.58</t>
+          <t>12534459785.1857</t>
         </is>
       </c>
       <c r="U23" t="inlineStr">
         <is>
-          <t>29.478</t>
+          <t>9263935752.74978</t>
         </is>
       </c>
       <c r="V23" t="inlineStr">
         <is>
-          <t>32.899</t>
+          <t>8865551471.97472</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Gross output (USD)</t>
+          <t>Working day of employee per year (magnitude of value)</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>gross_output.s.us</t>
+          <t>abstract_labour.empe.m.mv</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>3.253</t>
+          <t>1780.36002681152</t>
         </is>
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>3.521</t>
+          <t>1866.01851570889</t>
         </is>
       </c>
       <c r="J24" t="inlineStr">
         <is>
-          <t>3.812</t>
+          <t>1939.67840655153</t>
         </is>
       </c>
       <c r="K24" t="inlineStr">
         <is>
-          <t>4.456</t>
+          <t>1977.69867171003</t>
         </is>
       </c>
       <c r="L24" t="inlineStr">
         <is>
-          <t>5.438</t>
+          <t>1995.29409496824</t>
         </is>
       </c>
       <c r="M24" t="inlineStr">
         <is>
-          <t>6.707</t>
+          <t>1987.28113758021</t>
         </is>
       </c>
       <c r="N24" t="inlineStr">
         <is>
-          <t>8.178</t>
+          <t>1952.21723700909</t>
         </is>
       </c>
       <c r="O24" t="inlineStr">
         <is>
-          <t>10.654</t>
+          <t>1971.61638272585</t>
         </is>
       </c>
       <c r="P24" t="inlineStr">
         <is>
-          <t>13.69</t>
+          <t>2018.60118162499</t>
         </is>
       </c>
       <c r="Q24" t="inlineStr">
         <is>
-          <t>15.037</t>
+          <t>2027.39988628477</t>
         </is>
       </c>
       <c r="R24" t="inlineStr">
         <is>
-          <t>18.054</t>
+          <t>2035.32918314686</t>
         </is>
       </c>
       <c r="S24" t="inlineStr">
         <is>
-          <t>22.609</t>
+          <t>2066.17503381713</t>
         </is>
       </c>
       <c r="T24" t="inlineStr">
         <is>
-          <t>25.593</t>
+          <t>2072.19173498921</t>
         </is>
       </c>
       <c r="U24" t="inlineStr">
         <is>
-          <t>29.233</t>
+          <t>2080.82557999697</t>
         </is>
       </c>
       <c r="V24" t="inlineStr">
         <is>
-          <t>31.745</t>
+          <t>2085.57845055072</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Gross Domestic Product (USD)</t>
+          <t>Working day of persons engaged per year (magnitude of value)</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>gdp.s.us</t>
+          <t>abstract_labour.emp.m.mv</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>1.198</t>
+          <t>1780.36002681152</t>
         </is>
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>1.325</t>
+          <t>1866.01851570889</t>
         </is>
       </c>
       <c r="J25" t="inlineStr">
         <is>
-          <t>1.454</t>
+          <t>1939.67840655153</t>
         </is>
       </c>
       <c r="K25" t="inlineStr">
         <is>
-          <t>1.641</t>
+          <t>1977.69867171003</t>
         </is>
       </c>
       <c r="L25" t="inlineStr">
         <is>
-          <t>1.932</t>
+          <t>1995.29409496824</t>
         </is>
       </c>
       <c r="M25" t="inlineStr">
         <is>
-          <t>2.257</t>
+          <t>1987.28113758021</t>
         </is>
       </c>
       <c r="N25" t="inlineStr">
         <is>
-          <t>2.713</t>
+          <t>1952.21723700909</t>
         </is>
       </c>
       <c r="O25" t="inlineStr">
         <is>
-          <t>3.495</t>
+          <t>1971.61638272585</t>
         </is>
       </c>
       <c r="P25" t="inlineStr">
         <is>
-          <t>4.521</t>
+          <t>2018.60118162499</t>
         </is>
       </c>
       <c r="Q25" t="inlineStr">
         <is>
-          <t>4.99</t>
+          <t>2027.39988628477</t>
         </is>
       </c>
       <c r="R25" t="inlineStr">
         <is>
-          <t>5.931</t>
+          <t>2035.32918314686</t>
         </is>
       </c>
       <c r="S25" t="inlineStr">
         <is>
-          <t>7.363</t>
+          <t>2066.17503381713</t>
         </is>
       </c>
       <c r="T25" t="inlineStr">
         <is>
-          <t>8.319</t>
+          <t>2072.19173498921</t>
         </is>
       </c>
       <c r="U25" t="inlineStr">
         <is>
-          <t>9.38</t>
+          <t>2080.82557999697</t>
         </is>
       </c>
       <c r="V25" t="inlineStr">
         <is>
-          <t>10.284</t>
+          <t>2085.57845055072</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Rate of surplus value of high-skilled employee</t>
+          <t>Total exports (USD)</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>surplus_value.empe_hs.r.pc</t>
+          <t>exports.s.us</t>
+        </is>
+      </c>
+      <c r="H26" t="inlineStr">
+        <is>
+          <t>261938.018347437</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr">
+        <is>
+          <t>280419.776941541</t>
+        </is>
+      </c>
+      <c r="J26" t="inlineStr">
+        <is>
+          <t>345007.298581019</t>
+        </is>
+      </c>
+      <c r="K26" t="inlineStr">
+        <is>
+          <t>461968.459632732</t>
+        </is>
+      </c>
+      <c r="L26" t="inlineStr">
+        <is>
+          <t>632557.40360393</t>
+        </is>
+      </c>
+      <c r="M26" t="inlineStr">
+        <is>
+          <t>806873.985656646</t>
+        </is>
+      </c>
+      <c r="N26" t="inlineStr">
+        <is>
+          <t>1027619.28812731</t>
+        </is>
+      </c>
+      <c r="O26" t="inlineStr">
+        <is>
+          <t>1304801.79860809</t>
+        </is>
+      </c>
+      <c r="P26" t="inlineStr">
+        <is>
+          <t>1540785.17084099</t>
+        </is>
+      </c>
+      <c r="Q26" t="inlineStr">
+        <is>
+          <t>1293515.99451997</t>
+        </is>
+      </c>
+      <c r="R26" t="inlineStr">
+        <is>
+          <t>1697752.27422866</t>
+        </is>
+      </c>
+      <c r="S26" t="inlineStr">
+        <is>
+          <t>2037785.27696229</t>
+        </is>
+      </c>
+      <c r="T26" t="inlineStr">
+        <is>
+          <t>2156117.46640958</t>
+        </is>
+      </c>
+      <c r="U26" t="inlineStr">
+        <is>
+          <t>2293013.70422638</t>
+        </is>
+      </c>
+      <c r="V26" t="inlineStr">
+        <is>
+          <t>2425464.4149329</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Rate of surplus value of medium-skilled employee</t>
+          <t>Total exports (magnitude of value)</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>surplus_value.empe_ms.r.pc</t>
+          <t>exports.s.mv</t>
+        </is>
+      </c>
+      <c r="H27" t="inlineStr">
+        <is>
+          <t>138618058245.333</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr">
+        <is>
+          <t>137265182644.498</t>
+        </is>
+      </c>
+      <c r="J27" t="inlineStr">
+        <is>
+          <t>156361315573.417</t>
+        </is>
+      </c>
+      <c r="K27" t="inlineStr">
+        <is>
+          <t>192852194846.759</t>
+        </is>
+      </c>
+      <c r="L27" t="inlineStr">
+        <is>
+          <t>231660204350.66</t>
+        </is>
+      </c>
+      <c r="M27" t="inlineStr">
+        <is>
+          <t>266300391890.435</t>
+        </is>
+      </c>
+      <c r="N27" t="inlineStr">
+        <is>
+          <t>292526476967.126</t>
+        </is>
+      </c>
+      <c r="O27" t="inlineStr">
+        <is>
+          <t>299735659464.565</t>
+        </is>
+      </c>
+      <c r="P27" t="inlineStr">
+        <is>
+          <t>291515447314.536</t>
+        </is>
+      </c>
+      <c r="Q27" t="inlineStr">
+        <is>
+          <t>241626938875.71</t>
+        </is>
+      </c>
+      <c r="R27" t="inlineStr">
+        <is>
+          <t>263689967049.792</t>
+        </is>
+      </c>
+      <c r="S27" t="inlineStr">
+        <is>
+          <t>286424200494.02</t>
+        </is>
+      </c>
+      <c r="T27" t="inlineStr">
+        <is>
+          <t>278228465501.271</t>
+        </is>
+      </c>
+      <c r="U27" t="inlineStr">
+        <is>
+          <t>270557206041.25</t>
+        </is>
+      </c>
+      <c r="V27" t="inlineStr">
+        <is>
+          <t>260201875510.214</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Rate of surplus value of low-skilled employee</t>
+          <t>Total imports (USD)</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>surplus_value.empe_ls.r.pc</t>
+          <t>imports.s.us</t>
+        </is>
+      </c>
+      <c r="H28" t="inlineStr">
+        <is>
+          <t>220558.903536225</t>
+        </is>
+      </c>
+      <c r="I28" t="inlineStr">
+        <is>
+          <t>238471.973188644</t>
+        </is>
+      </c>
+      <c r="J28" t="inlineStr">
+        <is>
+          <t>289345.805299956</t>
+        </is>
+      </c>
+      <c r="K28" t="inlineStr">
+        <is>
+          <t>398624.650055453</t>
+        </is>
+      </c>
+      <c r="L28" t="inlineStr">
+        <is>
+          <t>542305.951931379</t>
+        </is>
+      </c>
+      <c r="M28" t="inlineStr">
+        <is>
+          <t>636852.598601152</t>
+        </is>
+      </c>
+      <c r="N28" t="inlineStr">
+        <is>
+          <t>765258.47093438</t>
+        </is>
+      </c>
+      <c r="O28" t="inlineStr">
+        <is>
+          <t>924493.15346435</t>
+        </is>
+      </c>
+      <c r="P28" t="inlineStr">
+        <is>
+          <t>1100033.98775197</t>
+        </is>
+      </c>
+      <c r="Q28" t="inlineStr">
+        <is>
+          <t>984359.709124691</t>
+        </is>
+      </c>
+      <c r="R28" t="inlineStr">
+        <is>
+          <t>1358267.11517569</t>
+        </is>
+      </c>
+      <c r="S28" t="inlineStr">
+        <is>
+          <t>1704024.77564393</t>
+        </is>
+      </c>
+      <c r="T28" t="inlineStr">
+        <is>
+          <t>1748573.32597829</t>
+        </is>
+      </c>
+      <c r="U28" t="inlineStr">
+        <is>
+          <t>1863450.36728005</t>
+        </is>
+      </c>
+      <c r="V28" t="inlineStr">
+        <is>
+          <t>1842837.00475207</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Hours of abstract labour</t>
+          <t>Total imports (magnitude of value)</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>abstract_labour.emp.s.mv</t>
+          <t>imports.s.mv</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>1281154.752</t>
+          <t>41492067998.9237</t>
         </is>
       </c>
       <c r="I29" t="inlineStr">
         <is>
-          <t>1358661.991</t>
+          <t>45368941422.1217</t>
         </is>
       </c>
       <c r="J29" t="inlineStr">
         <is>
-          <t>1430092.97</t>
+          <t>53044704808.642</t>
         </is>
       </c>
       <c r="K29" t="inlineStr">
         <is>
-          <t>1472458.079</t>
+          <t>69792075756.0869</t>
         </is>
       </c>
       <c r="L29" t="inlineStr">
         <is>
-          <t>1501021.793</t>
+          <t>85525920098.2525</t>
         </is>
       </c>
       <c r="M29" t="inlineStr">
         <is>
-          <t>1509876.006</t>
+          <t>90393728603.5103</t>
         </is>
       </c>
       <c r="N29" t="inlineStr">
         <is>
-          <t>1494135.694</t>
+          <t>98946096026.8558</t>
         </is>
       </c>
       <c r="O29" t="inlineStr">
         <is>
-          <t>1519893.748</t>
+          <t>99942550942.4258</t>
         </is>
       </c>
       <c r="P29" t="inlineStr">
         <is>
-          <t>1568479.449</t>
+          <t>108157443116.603</t>
         </is>
       </c>
       <c r="Q29" t="inlineStr">
         <is>
-          <t>1591354.705</t>
+          <t>97811200225.1334</t>
         </is>
       </c>
       <c r="R29" t="inlineStr">
         <is>
-          <t>1597046.567</t>
+          <t>123321268875.345</t>
         </is>
       </c>
       <c r="S29" t="inlineStr">
         <is>
-          <t>1736502.387</t>
+          <t>150037502607.559</t>
         </is>
       </c>
       <c r="T29" t="inlineStr">
         <is>
-          <t>1770099.919</t>
+          <t>156671006317.921</t>
         </is>
       </c>
       <c r="U29" t="inlineStr">
         <is>
-          <t>1784985.375</t>
+          <t>164715816677.921</t>
         </is>
       </c>
       <c r="V29" t="inlineStr">
         <is>
-          <t>1790192.448</t>
+          <t>168555192951.684</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Hours of abstract labour (employee only)</t>
+          <t>Trade balance (USD)</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>abstract_labour.empe.s.mv</t>
+          <t>trade_balance.s.us</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>484058.712</t>
+          <t>41379.1148112115</t>
         </is>
       </c>
       <c r="I30" t="inlineStr">
         <is>
-          <t>524443.508</t>
+          <t>41947.8037528966</t>
         </is>
       </c>
       <c r="J30" t="inlineStr">
         <is>
-          <t>563971.475</t>
+          <t>55661.4932810628</t>
         </is>
       </c>
       <c r="K30" t="inlineStr">
         <is>
-          <t>593106.096</t>
+          <t>63343.8095772788</t>
         </is>
       </c>
       <c r="L30" t="inlineStr">
         <is>
-          <t>617370.28</t>
+          <t>90251.4516725503</t>
         </is>
       </c>
       <c r="M30" t="inlineStr">
         <is>
-          <t>633936.541</t>
+          <t>170021.387055494</t>
         </is>
       </c>
       <c r="N30" t="inlineStr">
         <is>
-          <t>640117.6</t>
+          <t>262360.817192932</t>
         </is>
       </c>
       <c r="O30" t="inlineStr">
         <is>
-          <t>664178.389</t>
+          <t>380308.645143737</t>
         </is>
       </c>
       <c r="P30" t="inlineStr">
         <is>
-          <t>698883.052</t>
+          <t>440751.183089016</t>
         </is>
       </c>
       <c r="Q30" t="inlineStr">
         <is>
-          <t>722777.373</t>
+          <t>309156.285395284</t>
         </is>
       </c>
       <c r="R30" t="inlineStr">
         <is>
-          <t>739113.132</t>
+          <t>339485.159052967</t>
         </is>
       </c>
       <c r="S30" t="inlineStr">
         <is>
-          <t>818465.66</t>
+          <t>333760.501318356</t>
         </is>
       </c>
       <c r="T30" t="inlineStr">
         <is>
-          <t>849329.316</t>
+          <t>407544.140431294</t>
         </is>
       </c>
       <c r="U30" t="inlineStr">
         <is>
-          <t>871572.643</t>
+          <t>429563.336946327</t>
         </is>
       </c>
       <c r="V30" t="inlineStr">
         <is>
-          <t>889206.516</t>
+          <t>582627.41018083</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Gross output (magnitude of value)</t>
+          <t>Trade balance (magnitude of value)</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>gross_output.s.mv</t>
+          <t>trade_balance.s.mv</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>2071059.115</t>
+          <t>97125990246.4095</t>
         </is>
       </c>
       <c r="I31" t="inlineStr">
         <is>
-          <t>2027749.379</t>
+          <t>91896241222.3759</t>
         </is>
       </c>
       <c r="J31" t="inlineStr">
         <is>
-          <t>2027948.036</t>
+          <t>103316610764.775</t>
         </is>
       </c>
       <c r="K31" t="inlineStr">
         <is>
-          <t>2075980.695</t>
+          <t>123060119090.672</t>
         </is>
       </c>
       <c r="L31" t="inlineStr">
         <is>
-          <t>2151509.272</t>
+          <t>146134284252.408</t>
         </is>
       </c>
       <c r="M31" t="inlineStr">
         <is>
-          <t>2256495.604</t>
+          <t>175906663286.925</t>
         </is>
       </c>
       <c r="N31" t="inlineStr">
         <is>
-          <t>2428086.633</t>
+          <t>193580380940.27</t>
         </is>
       </c>
       <c r="O31" t="inlineStr">
         <is>
-          <t>2527290.885</t>
+          <t>199793108522.139</t>
         </is>
       </c>
       <c r="P31" t="inlineStr">
         <is>
-          <t>2685750.325</t>
+          <t>183358004197.933</t>
         </is>
       </c>
       <c r="Q31" t="inlineStr">
         <is>
-          <t>2852439.68</t>
+          <t>143815738650.576</t>
         </is>
       </c>
       <c r="R31" t="inlineStr">
         <is>
-          <t>2809953.338</t>
+          <t>140368698174.446</t>
         </is>
       </c>
       <c r="S31" t="inlineStr">
         <is>
-          <t>3122025.905</t>
+          <t>136386697886.461</t>
         </is>
       </c>
       <c r="T31" t="inlineStr">
         <is>
-          <t>3236448.452</t>
+          <t>121557459183.35</t>
         </is>
       </c>
       <c r="U31" t="inlineStr">
         <is>
-          <t>3283111.799</t>
+          <t>105841389363.33</t>
         </is>
       </c>
       <c r="V31" t="inlineStr">
         <is>
-          <t>3226896.522</t>
+          <t>91646682558.5302</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Gross output (direct prices - USD)</t>
+          <t>Gross Domestic Product of productive sectors (USD)</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>gross_output.s.du</t>
+          <t>gdp.p.s.us</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>16.828</t>
+          <t>854042.305133276</t>
         </is>
       </c>
       <c r="I32" t="inlineStr">
         <is>
-          <t>16.319</t>
+          <t>928727.79418407</t>
         </is>
       </c>
       <c r="J32" t="inlineStr">
         <is>
-          <t>16.418</t>
+          <t>1008001.60077362</t>
         </is>
       </c>
       <c r="K32" t="inlineStr">
         <is>
-          <t>18.292</t>
+          <t>1129248.95563351</t>
         </is>
       </c>
       <c r="L32" t="inlineStr">
         <is>
-          <t>20.96</t>
+          <t>1340976.65686878</t>
         </is>
       </c>
       <c r="M32" t="inlineStr">
         <is>
-          <t>23.602</t>
+          <t>1562777.21845455</t>
         </is>
       </c>
       <c r="N32" t="inlineStr">
         <is>
-          <t>26.832</t>
+          <t>1851357.58971296</t>
         </is>
       </c>
       <c r="O32" t="inlineStr">
         <is>
-          <t>31.529</t>
+          <t>2339648.29181658</t>
         </is>
       </c>
       <c r="P32" t="inlineStr">
         <is>
-          <t>36.369</t>
+          <t>3014636.28791816</t>
         </is>
       </c>
       <c r="Q32" t="inlineStr">
         <is>
-          <t>35.153</t>
+          <t>3247845.09471929</t>
         </is>
       </c>
       <c r="R32" t="inlineStr">
         <is>
-          <t>38.363</t>
+          <t>3859811.67370404</t>
         </is>
       </c>
       <c r="S32" t="inlineStr">
         <is>
-          <t>45.261</t>
+          <t>4804492.46312296</t>
         </is>
       </c>
       <c r="T32" t="inlineStr">
         <is>
-          <t>45.721</t>
+          <t>5357776.15435154</t>
         </is>
       </c>
       <c r="U32" t="inlineStr">
         <is>
-          <t>46.337</t>
+          <t>5947785.36677478</t>
         </is>
       </c>
       <c r="V32" t="inlineStr">
         <is>
-          <t>45.756</t>
+          <t>6440149.89963705</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>Gross Domestic Product (magnitude of value)</t>
+          <t>Rate of profit</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>gdp.s.mv</t>
+          <t>appropriated_profit.r.pc</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>994861.9</t>
+          <t>0.115191457014268</t>
         </is>
       </c>
       <c r="I33" t="inlineStr">
         <is>
-          <t>997553.185</t>
+          <t>0.114971963682422</t>
         </is>
       </c>
       <c r="J33" t="inlineStr">
         <is>
-          <t>1013999.359</t>
+          <t>0.111758622808971</t>
         </is>
       </c>
       <c r="K33" t="inlineStr">
         <is>
-          <t>999085.301</t>
+          <t>0.105891914956626</t>
         </is>
       </c>
       <c r="L33" t="inlineStr">
         <is>
-          <t>1001218.754</t>
+          <t>0.0999818506502773</t>
         </is>
       </c>
       <c r="M33" t="inlineStr">
         <is>
-          <t>999970.086</t>
+          <t>0.0976465792404536</t>
         </is>
       </c>
       <c r="N33" t="inlineStr">
         <is>
-          <t>1036806.039</t>
+          <t>0.104412967934683</t>
         </is>
       </c>
       <c r="O33" t="inlineStr">
         <is>
-          <t>1059170.482</t>
+          <t>0.121230548813236</t>
         </is>
       </c>
       <c r="P33" t="inlineStr">
         <is>
-          <t>1097415.175</t>
+          <t>0.10336467226376</t>
         </is>
       </c>
       <c r="Q33" t="inlineStr">
         <is>
-          <t>1109161.092</t>
+          <t>0.0903326809430535</t>
         </is>
       </c>
       <c r="R33" t="inlineStr">
         <is>
-          <t>1106283.494</t>
+          <t>0.082367705402171</t>
         </is>
       </c>
       <c r="S33" t="inlineStr">
         <is>
-          <t>1200325.632</t>
+          <t>0.0724161625030884</t>
         </is>
       </c>
       <c r="T33" t="inlineStr">
         <is>
-          <t>1207352.703</t>
+          <t>0.0593766063358975</t>
         </is>
       </c>
       <c r="U33" t="inlineStr">
         <is>
-          <t>1192792.842</t>
+          <t>0.0566920623572808</t>
         </is>
       </c>
       <c r="V33" t="inlineStr">
         <is>
-          <t>1169638.2</t>
+          <t>0.0537839390462959</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>Gross Domestic Product (direct prices - USD)</t>
+          <t>Compensation of employees (USD)</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>gdp.s.du</t>
+          <t>compensation.empe.s.us</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>8.083</t>
+          <t>588648.261561042</t>
         </is>
       </c>
       <c r="I34" t="inlineStr">
         <is>
-          <t>8.028</t>
+          <t>648537.417706858</t>
         </is>
       </c>
       <c r="J34" t="inlineStr">
         <is>
-          <t>8.209</t>
+          <t>708806.495508411</t>
         </is>
       </c>
       <c r="K34" t="inlineStr">
         <is>
-          <t>8.803</t>
+          <t>787189.110805554</t>
         </is>
       </c>
       <c r="L34" t="inlineStr">
         <is>
-          <t>9.754</t>
+          <t>923516.897971014</t>
         </is>
       </c>
       <c r="M34" t="inlineStr">
         <is>
-          <t>10.459</t>
+          <t>1059897.96776983</t>
         </is>
       </c>
       <c r="N34" t="inlineStr">
         <is>
-          <t>11.458</t>
+          <t>1251019.71548612</t>
         </is>
       </c>
       <c r="O34" t="inlineStr">
         <is>
-          <t>13.214</t>
+          <t>1588322.70451862</t>
         </is>
       </c>
       <c r="P34" t="inlineStr">
         <is>
-          <t>14.861</t>
+          <t>2157847.77481442</t>
         </is>
       </c>
       <c r="Q34" t="inlineStr">
         <is>
-          <t>13.669</t>
+          <t>2478568.29858374</t>
         </is>
       </c>
       <c r="R34" t="inlineStr">
         <is>
-          <t>15.103</t>
+          <t>3036441.33262075</t>
         </is>
       </c>
       <c r="S34" t="inlineStr">
         <is>
-          <t>17.402</t>
+          <t>3896981.0192003</t>
         </is>
       </c>
       <c r="T34" t="inlineStr">
         <is>
-          <t>17.056</t>
+          <t>4577126.62759297</t>
         </is>
       </c>
       <c r="U34" t="inlineStr">
         <is>
-          <t>16.835</t>
+          <t>5158719.31637214</t>
         </is>
       </c>
       <c r="V34" t="inlineStr">
         <is>
-          <t>16.585</t>
+          <t>5665835.26711</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>Total labour force value (magnitude of value)</t>
+          <t>Labour compensation (USD)</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>labour_force_value.s.mv</t>
+          <t>compensation.emp.s.us</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>502613.91</t>
+          <t>588648.261440248</t>
         </is>
       </c>
       <c r="I35" t="inlineStr">
         <is>
-          <t>509149.185</t>
+          <t>648537.417706858</t>
         </is>
       </c>
       <c r="J35" t="inlineStr">
         <is>
-          <t>527058.424</t>
+          <t>708806.495508411</t>
         </is>
       </c>
       <c r="K35" t="inlineStr">
         <is>
-          <t>510059.107</t>
+          <t>787189.110926371</t>
         </is>
       </c>
       <c r="L35" t="inlineStr">
         <is>
-          <t>508734.913</t>
+          <t>923516.897971014</t>
         </is>
       </c>
       <c r="M35" t="inlineStr">
         <is>
-          <t>490159.689</t>
+          <t>1059897.96776983</t>
         </is>
       </c>
       <c r="N35" t="inlineStr">
         <is>
-          <t>499655.154</t>
+          <t>1251019.71548612</t>
         </is>
       </c>
       <c r="O35" t="inlineStr">
         <is>
-          <t>484670.881</t>
+          <t>1588322.7047816</t>
         </is>
       </c>
       <c r="P35" t="inlineStr">
         <is>
-          <t>534315.695</t>
+          <t>2157847.77625412</t>
         </is>
       </c>
       <c r="Q35" t="inlineStr">
         <is>
-          <t>570917.195</t>
+          <t>2478568.3015114</t>
         </is>
       </c>
       <c r="R35" t="inlineStr">
         <is>
-          <t>568982.504</t>
+          <t>3036441.33114355</t>
         </is>
       </c>
       <c r="S35" t="inlineStr">
         <is>
-          <t>603629.121</t>
+          <t>3896981.0192003</t>
         </is>
       </c>
       <c r="T35" t="inlineStr">
         <is>
-          <t>640766.772</t>
+          <t>4577126.62759297</t>
         </is>
       </c>
       <c r="U35" t="inlineStr">
         <is>
-          <t>623564.781</t>
+          <t>5158719.31798628</t>
         </is>
       </c>
       <c r="V35" t="inlineStr">
         <is>
-          <t>625704.168</t>
+          <t>5665835.26711</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>Rate of surplus value</t>
+          <t>Capital stock (USD)</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>surplus_value.empe.r.pc</t>
+          <t>capital_stock.s.us</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>-3.69</t>
+          <t>2993742.86980939</t>
         </is>
       </c>
       <c r="I36" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>3358259.88283325</t>
         </is>
       </c>
       <c r="J36" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>3787643.71776461</t>
         </is>
       </c>
       <c r="K36" t="inlineStr">
         <is>
-          <t>16.28</t>
+          <t>4422157.31166924</t>
         </is>
       </c>
       <c r="L36" t="inlineStr">
         <is>
-          <t>21.35</t>
+          <t>5325574.17921317</t>
         </is>
       </c>
       <c r="M36" t="inlineStr">
         <is>
-          <t>29.33</t>
+          <t>6376393.7018432</t>
         </is>
       </c>
       <c r="N36" t="inlineStr">
         <is>
-          <t>28.11</t>
+          <t>7635752.34695555</t>
         </is>
       </c>
       <c r="O36" t="inlineStr">
         <is>
-          <t>37.04</t>
+          <t>9346399.27334974</t>
         </is>
       </c>
       <c r="P36" t="inlineStr">
         <is>
-          <t>30.8</t>
+          <t>12592008.0238074</t>
         </is>
       </c>
       <c r="Q36" t="inlineStr">
         <is>
-          <t>26.6</t>
+          <t>14292423.3597335</t>
         </is>
       </c>
       <c r="R36" t="inlineStr">
         <is>
-          <t>29.9</t>
+          <t>17111423.3990992</t>
         </is>
       </c>
       <c r="S36" t="inlineStr">
         <is>
-          <t>35.59</t>
+          <t>21876816.7470749</t>
         </is>
       </c>
       <c r="T36" t="inlineStr">
         <is>
-          <t>32.55</t>
+          <t>25580489.5361577</t>
         </is>
       </c>
       <c r="U36" t="inlineStr">
         <is>
-          <t>39.77</t>
+          <t>29478137.609998</t>
         </is>
       </c>
       <c r="V36" t="inlineStr">
         <is>
-          <t>42.11</t>
+          <t>32898860.3425465</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>Value per output</t>
+          <t>Total real wage (constant USD)</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>value.m.mv</t>
+          <t>compensation.emp.s.cu</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>23.021</t>
+          <t>1109163.86570766</t>
         </is>
       </c>
       <c r="I37" t="inlineStr">
         <is>
-          <t>20.843</t>
+          <t>1153816.65605986</t>
         </is>
       </c>
       <c r="J37" t="inlineStr">
         <is>
-          <t>19.461</t>
+          <t>1223284.68524949</t>
         </is>
       </c>
       <c r="K37" t="inlineStr">
         <is>
-          <t>17.711</t>
+          <t>1271141.65320255</t>
         </is>
       </c>
       <c r="L37" t="inlineStr">
         <is>
-          <t>15.32</t>
+          <t>1349759.74063459</t>
         </is>
       </c>
       <c r="M37" t="inlineStr">
         <is>
-          <t>13.357</t>
+          <t>1478037.03340391</t>
         </is>
       </c>
       <c r="N37" t="inlineStr">
         <is>
-          <t>11.894</t>
+          <t>1633268.63422483</t>
         </is>
       </c>
       <c r="O37" t="inlineStr">
         <is>
-          <t>9.477</t>
+          <t>1782213.29766099</t>
         </is>
       </c>
       <c r="P37" t="inlineStr">
         <is>
-          <t>7.913</t>
+          <t>1995887.46387921</t>
         </is>
       </c>
       <c r="Q37" t="inlineStr">
         <is>
-          <t>7.602</t>
+          <t>2165414.0577308</t>
         </is>
       </c>
       <c r="R37" t="inlineStr">
         <is>
-          <t>6.413</t>
+          <t>2482967.03960229</t>
         </is>
       </c>
       <c r="S37" t="inlineStr">
         <is>
-          <t>5.641</t>
+          <t>2803147.01312853</t>
         </is>
       </c>
       <c r="T37" t="inlineStr">
         <is>
-          <t>5.123</t>
+          <t>3131859.45936727</t>
         </is>
       </c>
       <c r="U37" t="inlineStr">
         <is>
-          <t>4.546</t>
+          <t>3363197.49428672</t>
         </is>
       </c>
       <c r="V37" t="inlineStr">
         <is>
-          <t>4.153</t>
+          <t>3633957.83455807</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>Total real compensation of labour (constant USD)</t>
+        </is>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>compensation.empe.s.cu</t>
+        </is>
+      </c>
+      <c r="H38" t="inlineStr">
+        <is>
+          <t>1109163.86578011</t>
+        </is>
+      </c>
+      <c r="I38" t="inlineStr">
+        <is>
+          <t>1153816.65605986</t>
+        </is>
+      </c>
+      <c r="J38" t="inlineStr">
+        <is>
+          <t>1223284.68524949</t>
+        </is>
+      </c>
+      <c r="K38" t="inlineStr">
+        <is>
+          <t>1271141.65304819</t>
+        </is>
+      </c>
+      <c r="L38" t="inlineStr">
+        <is>
+          <t>1349759.74063459</t>
+        </is>
+      </c>
+      <c r="M38" t="inlineStr">
+        <is>
+          <t>1478037.03336184</t>
+        </is>
+      </c>
+      <c r="N38" t="inlineStr">
+        <is>
+          <t>1633268.634196</t>
+        </is>
+      </c>
+      <c r="O38" t="inlineStr">
+        <is>
+          <t>1782213.29772046</t>
+        </is>
+      </c>
+      <c r="P38" t="inlineStr">
+        <is>
+          <t>1995887.4622481</t>
+        </is>
+      </c>
+      <c r="Q38" t="inlineStr">
+        <is>
+          <t>2165414.05512831</t>
+        </is>
+      </c>
+      <c r="R38" t="inlineStr">
+        <is>
+          <t>2482967.04081023</t>
+        </is>
+      </c>
+      <c r="S38" t="inlineStr">
+        <is>
+          <t>2803147.01312853</t>
+        </is>
+      </c>
+      <c r="T38" t="inlineStr">
+        <is>
+          <t>3131859.45936727</t>
+        </is>
+      </c>
+      <c r="U38" t="inlineStr">
+        <is>
+          <t>3363197.49315615</t>
+        </is>
+      </c>
+      <c r="V38" t="inlineStr">
+        <is>
+          <t>3633957.83455807</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>Total profit (USD)</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>profit.s.us</t>
+        </is>
+      </c>
+      <c r="H39" t="inlineStr">
+        <is>
+          <t>609804.028410245</t>
+        </is>
+      </c>
+      <c r="I39" t="inlineStr">
+        <is>
+          <t>676294.413002177</t>
+        </is>
+      </c>
+      <c r="J39" t="inlineStr">
+        <is>
+          <t>745004.929268195</t>
+        </is>
+      </c>
+      <c r="K39" t="inlineStr">
+        <is>
+          <t>853780.684462076</t>
+        </is>
+      </c>
+      <c r="L39" t="inlineStr">
+        <is>
+          <t>1008101.21462393</t>
+        </is>
+      </c>
+      <c r="M39" t="inlineStr">
+        <is>
+          <t>1197262.61929072</t>
+        </is>
+      </c>
+      <c r="N39" t="inlineStr">
+        <is>
+          <t>1462167.31533039</t>
+        </is>
+      </c>
+      <c r="O39" t="inlineStr">
+        <is>
+          <t>1906737.27747094</t>
+        </is>
+      </c>
+      <c r="P39" t="inlineStr">
+        <is>
+          <t>2363464.19384793</t>
+        </is>
+      </c>
+      <c r="Q39" t="inlineStr">
+        <is>
+          <t>2511669.35189861</t>
+        </is>
+      </c>
+      <c r="R39" t="inlineStr">
+        <is>
+          <t>2894705.73047374</t>
+        </is>
+      </c>
+      <c r="S39" t="inlineStr">
+        <is>
+          <t>3465949.73436733</t>
+        </is>
+      </c>
+      <c r="T39" t="inlineStr">
+        <is>
+          <t>3741665.95171963</t>
+        </is>
+      </c>
+      <c r="U39" t="inlineStr">
+        <is>
+          <t>4221639.24651976</t>
+        </is>
+      </c>
+      <c r="V39" t="inlineStr">
+        <is>
+          <t>4618147.79603863</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>Hours of abstract labour (employee only)</t>
+        </is>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>abstract_labour.empe.s.mv</t>
+        </is>
+      </c>
+      <c r="H40" t="inlineStr">
+        <is>
+          <t>484058712196.965</t>
+        </is>
+      </c>
+      <c r="I40" t="inlineStr">
+        <is>
+          <t>524443507580.079</t>
+        </is>
+      </c>
+      <c r="J40" t="inlineStr">
+        <is>
+          <t>563971475298.109</t>
+        </is>
+      </c>
+      <c r="K40" t="inlineStr">
+        <is>
+          <t>593106096064.014</t>
+        </is>
+      </c>
+      <c r="L40" t="inlineStr">
+        <is>
+          <t>617370279587.777</t>
+        </is>
+      </c>
+      <c r="M40" t="inlineStr">
+        <is>
+          <t>633936540633.373</t>
+        </is>
+      </c>
+      <c r="N40" t="inlineStr">
+        <is>
+          <t>640117599753.073</t>
+        </is>
+      </c>
+      <c r="O40" t="inlineStr">
+        <is>
+          <t>664178388837.835</t>
+        </is>
+      </c>
+      <c r="P40" t="inlineStr">
+        <is>
+          <t>698883051759.265</t>
+        </is>
+      </c>
+      <c r="Q40" t="inlineStr">
+        <is>
+          <t>722777372945.087</t>
+        </is>
+      </c>
+      <c r="R40" t="inlineStr">
+        <is>
+          <t>739113131531.172</t>
+        </is>
+      </c>
+      <c r="S40" t="inlineStr">
+        <is>
+          <t>818465660151.383</t>
+        </is>
+      </c>
+      <c r="T40" t="inlineStr">
+        <is>
+          <t>849329315738.673</t>
+        </is>
+      </c>
+      <c r="U40" t="inlineStr">
+        <is>
+          <t>871572642855.397</t>
+        </is>
+      </c>
+      <c r="V40" t="inlineStr">
+        <is>
+          <t>889206516354.598</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>Hours of abstract labour</t>
+        </is>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>abstract_labour.emp.s.mv</t>
+        </is>
+      </c>
+      <c r="H41" t="inlineStr">
+        <is>
+          <t>1281154752206.01</t>
+        </is>
+      </c>
+      <c r="I41" t="inlineStr">
+        <is>
+          <t>1358661990589.66</t>
+        </is>
+      </c>
+      <c r="J41" t="inlineStr">
+        <is>
+          <t>1430092969802.58</t>
+        </is>
+      </c>
+      <c r="K41" t="inlineStr">
+        <is>
+          <t>1472458078520.36</t>
+        </is>
+      </c>
+      <c r="L41" t="inlineStr">
+        <is>
+          <t>1501021793160.33</t>
+        </is>
+      </c>
+      <c r="M41" t="inlineStr">
+        <is>
+          <t>1509876005638.66</t>
+        </is>
+      </c>
+      <c r="N41" t="inlineStr">
+        <is>
+          <t>1494135693822.33</t>
+        </is>
+      </c>
+      <c r="O41" t="inlineStr">
+        <is>
+          <t>1519893747974.16</t>
+        </is>
+      </c>
+      <c r="P41" t="inlineStr">
+        <is>
+          <t>1568479448756.43</t>
+        </is>
+      </c>
+      <c r="Q41" t="inlineStr">
+        <is>
+          <t>1591354704670.79</t>
+        </is>
+      </c>
+      <c r="R41" t="inlineStr">
+        <is>
+          <t>1597046566584.14</t>
+        </is>
+      </c>
+      <c r="S41" t="inlineStr">
+        <is>
+          <t>1736502387336.04</t>
+        </is>
+      </c>
+      <c r="T41" t="inlineStr">
+        <is>
+          <t>1770099919453.61</t>
+        </is>
+      </c>
+      <c r="U41" t="inlineStr">
+        <is>
+          <t>1784985374665.7</t>
+        </is>
+      </c>
+      <c r="V41" t="inlineStr">
+        <is>
+          <t>1790192447816.32</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>Gross Domestic Product (magnitude of value)</t>
+        </is>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>gdp.s.mv</t>
+        </is>
+      </c>
+      <c r="H42" t="inlineStr">
+        <is>
+          <t>994861900174.557</t>
+        </is>
+      </c>
+      <c r="I42" t="inlineStr">
+        <is>
+          <t>997553185289.72</t>
+        </is>
+      </c>
+      <c r="J42" t="inlineStr">
+        <is>
+          <t>1013999359191.35</t>
+        </is>
+      </c>
+      <c r="K42" t="inlineStr">
+        <is>
+          <t>999085301380.989</t>
+        </is>
+      </c>
+      <c r="L42" t="inlineStr">
+        <is>
+          <t>1001218754043.79</t>
+        </is>
+      </c>
+      <c r="M42" t="inlineStr">
+        <is>
+          <t>999970086166.46</t>
+        </is>
+      </c>
+      <c r="N42" t="inlineStr">
+        <is>
+          <t>1036806039292.88</t>
+        </is>
+      </c>
+      <c r="O42" t="inlineStr">
+        <is>
+          <t>1059170481631.55</t>
+        </is>
+      </c>
+      <c r="P42" t="inlineStr">
+        <is>
+          <t>1097415174565.54</t>
+        </is>
+      </c>
+      <c r="Q42" t="inlineStr">
+        <is>
+          <t>1109161092311.59</t>
+        </is>
+      </c>
+      <c r="R42" t="inlineStr">
+        <is>
+          <t>1106283493817.43</t>
+        </is>
+      </c>
+      <c r="S42" t="inlineStr">
+        <is>
+          <t>1200325632096.01</t>
+        </is>
+      </c>
+      <c r="T42" t="inlineStr">
+        <is>
+          <t>1207352703299.81</t>
+        </is>
+      </c>
+      <c r="U42" t="inlineStr">
+        <is>
+          <t>1192792841732.42</t>
+        </is>
+      </c>
+      <c r="V42" t="inlineStr">
+        <is>
+          <t>1169638200430.26</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>Number of persons engaged</t>
+        </is>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>emp.s.un</t>
+        </is>
+      </c>
+      <c r="H43" t="inlineStr">
+        <is>
+          <t>719604312</t>
+        </is>
+      </c>
+      <c r="I43" t="inlineStr">
+        <is>
+          <t>728107454</t>
+        </is>
+      </c>
+      <c r="J43" t="inlineStr">
+        <is>
+          <t>737283544</t>
+        </is>
+      </c>
+      <c r="K43" t="inlineStr">
+        <is>
+          <t>744531055</t>
+        </is>
+      </c>
+      <c r="L43" t="inlineStr">
+        <is>
+          <t>752280978</t>
+        </is>
+      </c>
+      <c r="M43" t="inlineStr">
+        <is>
+          <t>759769706</t>
+        </is>
+      </c>
+      <c r="N43" t="inlineStr">
+        <is>
+          <t>765353192</t>
+        </is>
+      </c>
+      <c r="O43" t="inlineStr">
+        <is>
+          <t>770887157</t>
+        </is>
+      </c>
+      <c r="P43" t="inlineStr">
+        <is>
+          <t>777013044</t>
+        </is>
+      </c>
+      <c r="Q43" t="inlineStr">
+        <is>
+          <t>784923939</t>
+        </is>
+      </c>
+      <c r="R43" t="inlineStr">
+        <is>
+          <t>784662540</t>
+        </is>
+      </c>
+      <c r="S43" t="inlineStr">
+        <is>
+          <t>840443021</t>
+        </is>
+      </c>
+      <c r="T43" t="inlineStr">
+        <is>
+          <t>854216282</t>
+        </is>
+      </c>
+      <c r="U43" t="inlineStr">
+        <is>
+          <t>857825563</t>
+        </is>
+      </c>
+      <c r="V43" t="inlineStr">
+        <is>
+          <t>858367350</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>Number of employee</t>
+        </is>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>empe.s.un</t>
+        </is>
+      </c>
+      <c r="H44" t="inlineStr">
+        <is>
+          <t>271888104.039201</t>
+        </is>
+      </c>
+      <c r="I44" t="inlineStr">
+        <is>
+          <t>281049466.103956</t>
+        </is>
+      </c>
+      <c r="J44" t="inlineStr">
+        <is>
+          <t>290755144.457565</t>
+        </is>
+      </c>
+      <c r="K44" t="inlineStr">
+        <is>
+          <t>299897099.870721</t>
+        </is>
+      </c>
+      <c r="L44" t="inlineStr">
+        <is>
+          <t>309413174.300806</t>
+        </is>
+      </c>
+      <c r="M44" t="inlineStr">
+        <is>
+          <t>318996909.217022</t>
+        </is>
+      </c>
+      <c r="N44" t="inlineStr">
+        <is>
+          <t>327892607.245785</t>
+        </is>
+      </c>
+      <c r="O44" t="inlineStr">
+        <is>
+          <t>336869988.836052</t>
+        </is>
+      </c>
+      <c r="P44" t="inlineStr">
+        <is>
+          <t>346221461.733545</t>
+        </is>
+      </c>
+      <c r="Q44" t="inlineStr">
+        <is>
+          <t>356504593.807384</t>
+        </is>
+      </c>
+      <c r="R44" t="inlineStr">
+        <is>
+          <t>363141813.939117</t>
+        </is>
+      </c>
+      <c r="S44" t="inlineStr">
+        <is>
+          <t>396126004.21336</t>
+        </is>
+      </c>
+      <c r="T44" t="inlineStr">
+        <is>
+          <t>409870043.103466</t>
+        </is>
+      </c>
+      <c r="U44" t="inlineStr">
+        <is>
+          <t>418859058.266992</t>
+        </is>
+      </c>
+      <c r="V44" t="inlineStr">
+        <is>
+          <t>426359658.693153</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>Total hours worked by persons engaged</t>
+        </is>
+      </c>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>hours_worked.emp.s.hr</t>
+        </is>
+      </c>
+      <c r="H45" t="inlineStr">
+        <is>
+          <t>1281154752206.01</t>
+        </is>
+      </c>
+      <c r="I45" t="inlineStr">
+        <is>
+          <t>1358661990589.66</t>
+        </is>
+      </c>
+      <c r="J45" t="inlineStr">
+        <is>
+          <t>1430092969802.58</t>
+        </is>
+      </c>
+      <c r="K45" t="inlineStr">
+        <is>
+          <t>1472458078520.36</t>
+        </is>
+      </c>
+      <c r="L45" t="inlineStr">
+        <is>
+          <t>1501021793160.33</t>
+        </is>
+      </c>
+      <c r="M45" t="inlineStr">
+        <is>
+          <t>1509876005638.66</t>
+        </is>
+      </c>
+      <c r="N45" t="inlineStr">
+        <is>
+          <t>1494135693822.33</t>
+        </is>
+      </c>
+      <c r="O45" t="inlineStr">
+        <is>
+          <t>1519893747974.16</t>
+        </is>
+      </c>
+      <c r="P45" t="inlineStr">
+        <is>
+          <t>1568479448756.43</t>
+        </is>
+      </c>
+      <c r="Q45" t="inlineStr">
+        <is>
+          <t>1591354704670.79</t>
+        </is>
+      </c>
+      <c r="R45" t="inlineStr">
+        <is>
+          <t>1597046566584.14</t>
+        </is>
+      </c>
+      <c r="S45" t="inlineStr">
+        <is>
+          <t>1736502387336.04</t>
+        </is>
+      </c>
+      <c r="T45" t="inlineStr">
+        <is>
+          <t>1770099919453.61</t>
+        </is>
+      </c>
+      <c r="U45" t="inlineStr">
+        <is>
+          <t>1784985374665.7</t>
+        </is>
+      </c>
+      <c r="V45" t="inlineStr">
+        <is>
+          <t>1790192447816.32</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>Total hours worked by employees</t>
+        </is>
+      </c>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>hours_worked.empe.s.hr</t>
+        </is>
+      </c>
+      <c r="H46" t="inlineStr">
+        <is>
+          <t>484058712196.965</t>
+        </is>
+      </c>
+      <c r="I46" t="inlineStr">
+        <is>
+          <t>524443507580.079</t>
+        </is>
+      </c>
+      <c r="J46" t="inlineStr">
+        <is>
+          <t>563971475298.109</t>
+        </is>
+      </c>
+      <c r="K46" t="inlineStr">
+        <is>
+          <t>593106096064.014</t>
+        </is>
+      </c>
+      <c r="L46" t="inlineStr">
+        <is>
+          <t>617370279587.777</t>
+        </is>
+      </c>
+      <c r="M46" t="inlineStr">
+        <is>
+          <t>633936540633.373</t>
+        </is>
+      </c>
+      <c r="N46" t="inlineStr">
+        <is>
+          <t>640117599753.073</t>
+        </is>
+      </c>
+      <c r="O46" t="inlineStr">
+        <is>
+          <t>664178388837.835</t>
+        </is>
+      </c>
+      <c r="P46" t="inlineStr">
+        <is>
+          <t>698883051759.265</t>
+        </is>
+      </c>
+      <c r="Q46" t="inlineStr">
+        <is>
+          <t>722777372945.087</t>
+        </is>
+      </c>
+      <c r="R46" t="inlineStr">
+        <is>
+          <t>739113131531.172</t>
+        </is>
+      </c>
+      <c r="S46" t="inlineStr">
+        <is>
+          <t>818465660151.383</t>
+        </is>
+      </c>
+      <c r="T46" t="inlineStr">
+        <is>
+          <t>849329315738.673</t>
+        </is>
+      </c>
+      <c r="U46" t="inlineStr">
+        <is>
+          <t>871572642855.397</t>
+        </is>
+      </c>
+      <c r="V46" t="inlineStr">
+        <is>
+          <t>889206516354.598</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>Share of high-skilled labour compensation</t>
+        </is>
+      </c>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>compensation.empe_hs.r.pc</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>Share of medium-skilled labour compensation</t>
+        </is>
+      </c>
+      <c r="B48" t="inlineStr">
+        <is>
+          <t>compensation.empe_ms.r.pc</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
+          <t>Share of low-skilled labour compensation</t>
+        </is>
+      </c>
+      <c r="B49" t="inlineStr">
+        <is>
+          <t>compensation.empe_ls.r.pc</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="inlineStr">
+        <is>
+          <t>Share of hours worked by high-skilled persons engaged</t>
+        </is>
+      </c>
+      <c r="B50" t="inlineStr">
+        <is>
+          <t>hours_worked.empe_hs.r.pc</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="inlineStr">
+        <is>
+          <t>Share of hours worked by medium-skilled persons engaged</t>
+        </is>
+      </c>
+      <c r="B51" t="inlineStr">
+        <is>
+          <t>hours_worked.empe_ms.r.pc</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="inlineStr">
+        <is>
+          <t>Share of hours worked by low-skilled persons engaged</t>
+        </is>
+      </c>
+      <c r="B52" t="inlineStr">
+        <is>
+          <t>hours_worked.empe_ls.r.pc</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="inlineStr">
+        <is>
+          <t>Gross output (USD)</t>
+        </is>
+      </c>
+      <c r="B53" t="inlineStr">
+        <is>
+          <t>gross_output.s.us</t>
+        </is>
+      </c>
+      <c r="H53" t="inlineStr">
+        <is>
+          <t>3253015.70227797</t>
+        </is>
+      </c>
+      <c r="I53" t="inlineStr">
+        <is>
+          <t>3521177.91153665</t>
+        </is>
+      </c>
+      <c r="J53" t="inlineStr">
+        <is>
+          <t>3812211.86576439</t>
+        </is>
+      </c>
+      <c r="K53" t="inlineStr">
+        <is>
+          <t>4455647.71315393</t>
+        </is>
+      </c>
+      <c r="L53" t="inlineStr">
+        <is>
+          <t>5437770.06408265</t>
+        </is>
+      </c>
+      <c r="M53" t="inlineStr">
+        <is>
+          <t>6707046.56430474</t>
+        </is>
+      </c>
+      <c r="N53" t="inlineStr">
+        <is>
+          <t>8177587.50590138</t>
+        </is>
+      </c>
+      <c r="O53" t="inlineStr">
+        <is>
+          <t>10654372.3158218</t>
+        </is>
+      </c>
+      <c r="P53" t="inlineStr">
+        <is>
+          <t>13689958.4413456</t>
+        </is>
+      </c>
+      <c r="Q53" t="inlineStr">
+        <is>
+          <t>15036959.8810756</t>
+        </is>
+      </c>
+      <c r="R53" t="inlineStr">
+        <is>
+          <t>18053714.464996</t>
+        </is>
+      </c>
+      <c r="S53" t="inlineStr">
+        <is>
+          <t>22608922.70497</t>
+        </is>
+      </c>
+      <c r="T53" t="inlineStr">
+        <is>
+          <t>25593234.4224765</t>
+        </is>
+      </c>
+      <c r="U53" t="inlineStr">
+        <is>
+          <t>29232642.460012</t>
+        </is>
+      </c>
+      <c r="V53" t="inlineStr">
+        <is>
+          <t>31745102.4312362</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="inlineStr">
+        <is>
+          <t>Gross Domestic Product (USD)</t>
+        </is>
+      </c>
+      <c r="B54" t="inlineStr">
+        <is>
+          <t>gdp.s.us</t>
+        </is>
+      </c>
+      <c r="H54" t="inlineStr">
+        <is>
+          <t>1198452.28731382</t>
+        </is>
+      </c>
+      <c r="I54" t="inlineStr">
+        <is>
+          <t>1324831.83964957</t>
+        </is>
+      </c>
+      <c r="J54" t="inlineStr">
+        <is>
+          <t>1453811.41873581</t>
+        </is>
+      </c>
+      <c r="K54" t="inlineStr">
+        <is>
+          <t>1640969.79297211</t>
+        </is>
+      </c>
+      <c r="L54" t="inlineStr">
+        <is>
+          <t>1931618.10305032</t>
+        </is>
+      </c>
+      <c r="M54" t="inlineStr">
+        <is>
+          <t>2257160.588159</t>
+        </is>
+      </c>
+      <c r="N54" t="inlineStr">
+        <is>
+          <t>2713187.017772</t>
+        </is>
+      </c>
+      <c r="O54" t="inlineStr">
+        <is>
+          <t>3495059.9684464</t>
+        </is>
+      </c>
+      <c r="P54" t="inlineStr">
+        <is>
+          <t>4521311.99515283</t>
+        </is>
+      </c>
+      <c r="Q54" t="inlineStr">
+        <is>
+          <t>4990237.6414066</t>
+        </is>
+      </c>
+      <c r="R54" t="inlineStr">
+        <is>
+          <t>5931147.01080161</t>
+        </is>
+      </c>
+      <c r="S54" t="inlineStr">
+        <is>
+          <t>7362930.74985253</t>
+        </is>
+      </c>
+      <c r="T54" t="inlineStr">
+        <is>
+          <t>8318792.56141102</t>
+        </is>
+      </c>
+      <c r="U54" t="inlineStr">
+        <is>
+          <t>9380358.56434463</t>
+        </is>
+      </c>
+      <c r="V54" t="inlineStr">
+        <is>
+          <t>10283983.0468709</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="B55" t="inlineStr">
+        <is>
+          <t>capital_stock.s.cu</t>
+        </is>
+      </c>
+      <c r="H55" t="inlineStr">
+        <is>
+          <t>4919624.03745587</t>
+        </is>
+      </c>
+      <c r="I55" t="inlineStr">
+        <is>
+          <t>5396581.55777743</t>
+        </is>
+      </c>
+      <c r="J55" t="inlineStr">
+        <is>
+          <t>5988833.77341301</t>
+        </is>
+      </c>
+      <c r="K55" t="inlineStr">
+        <is>
+          <t>6718674.5767622</t>
+        </is>
+      </c>
+      <c r="L55" t="inlineStr">
+        <is>
+          <t>7491983.49042179</t>
+        </is>
+      </c>
+      <c r="M55" t="inlineStr">
+        <is>
+          <t>8408410.87669791</t>
+        </is>
+      </c>
+      <c r="N55" t="inlineStr">
+        <is>
+          <t>9368539.06279825</t>
+        </is>
+      </c>
+      <c r="O55" t="inlineStr">
+        <is>
+          <t>10234712.2328434</t>
+        </is>
+      </c>
+      <c r="P55" t="inlineStr">
+        <is>
+          <t>11758757.5018991</t>
+        </is>
+      </c>
+      <c r="Q55" t="inlineStr">
+        <is>
+          <t>12759887.5674895</t>
+        </is>
+      </c>
+      <c r="R55" t="inlineStr">
+        <is>
+          <t>13992399.5353852</t>
+        </is>
+      </c>
+      <c r="S55" t="inlineStr">
+        <is>
+          <t>15839810.5692754</t>
+        </is>
+      </c>
+      <c r="T55" t="inlineStr">
+        <is>
+          <t>17635255.1185056</t>
+        </is>
+      </c>
+      <c r="U55" t="inlineStr">
+        <is>
+          <t>19306413.0707955</t>
+        </is>
+      </c>
+      <c r="V55" t="inlineStr">
+        <is>
+          <t>21206564.5748714</t>
         </is>
       </c>
     </row>
@@ -2699,7 +4265,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:C32"/>
+  <dimension ref="A1:C49"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2722,36 +4288,51 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Capital depreciation (USD)</t>
+          <t>Hours of abstract labour</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>capital_depreciation.s.us</t>
+          <t>abstract_labour.emp.s.mv</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Hours of abstract labour</t>
+          <t>Hours of abstract labour (employee only)</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>abstract_labour.emp.s.mv</t>
+          <t>abstract_labour.empe.s.mv</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Hours of abstract labour (employee only)</t>
+          <t>Number of persons engaged</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>abstract_labour.empe.s.mv</t>
+          <t>emp.s.un</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
@@ -2763,331 +4344,695 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>emp.s.un</t>
+          <t>empe.s.un</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Number of persons engaged</t>
+          <t>Total hours worked by persons engaged</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>empe.s.un</t>
+          <t>hours_worked.emp.s.hr</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Total hours worked by persons engaged</t>
+          <t>Total hours worked by employees</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>hours_worked.emp.s.hr</t>
+          <t>hours_worked.empe.s.hr</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Total hours worked by employees</t>
+          <t>Share of hours worked by high-skilled persons engaged</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>hours_worked.empe.s.hr</t>
+          <t>hours_worked.empe_hs.r.pc</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Share of high-skilled labour compensation</t>
+          <t>Share of hours worked by medium-skilled persons engaged</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>compensation.empe_hs.r.pc</t>
+          <t>hours_worked.empe_ms.r.pc</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Share of medium-skilled labour compensation</t>
+          <t>Share of hours worked by low-skilled persons engaged</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>compensation.empe_ms.r.pc</t>
+          <t>hours_worked.empe_ls.r.pc</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Share of low-skilled labour compensation</t>
+          <t>Share of high-skilled labour compensation</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>compensation.empe_ls.r.pc</t>
+          <t>compensation.empe_hs.r.pc</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Share of hours worked by high-skilled persons engaged</t>
+          <t>Share of medium-skilled labour compensation</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>hours_worked.empe_hs.r.pc</t>
+          <t>compensation.empe_ms.r.pc</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Share of hours worked by medium-skilled persons engaged</t>
+          <t>Share of low-skilled labour compensation</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>hours_worked.empe_ms.r.pc</t>
+          <t>compensation.empe_ls.r.pc</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Share of hours worked by low-skilled persons engaged</t>
+          <t>Compensation of employees (USD)</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>hours_worked.empe_ls.r.pc</t>
+          <t>compensation.empe.s.us</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Exchange rate (USD)</t>
+          <t>Labour compensation (USD)</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>exchange.r.us</t>
+          <t>compensation.emp.s.us</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Compensation of employees (USD)</t>
+          <t>Total labour force value (magnitude of value)</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>compensation.empe.s.us</t>
+          <t>labour_force_value.s.mv</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Labour compensation (USD)</t>
+          <t>Labour force value (magnitude of value)</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>compensation.emp.s.us</t>
+          <t>labour_force_value.m.mv</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Capital stock (USD)</t>
+          <t>Capital depreciation (USD)</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>capital_stock.s.us</t>
+          <t>capital_depreciation.s.us</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Gross output (USD)</t>
+          <t>Capital stock (USD)</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>gross_output.s.us</t>
+          <t>capital_stock.s.us</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Gross output (magnitude of value)</t>
+          <t>Rate of surplus value</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>gross_output.s.mv</t>
+          <t>surplus_value.empe.r.pc</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Gross output (direct prices - USD)</t>
+          <t>Rate of surplus value of high-skilled employee</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>gross_output.s.du</t>
+          <t>surplus_value.empe_hs.r.pc</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Total labour force value (magnitude of value)</t>
+          <t>Rate of surplus value of medium-skilled employee</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>labour_force_value.s.mv</t>
+          <t>surplus_value.empe_ms.r.pc</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Rate of surplus value</t>
+          <t>Rate of surplus value of low-skilled employee</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>surplus_value.empe.r.pc</t>
+          <t>surplus_value.empe_ls.r.pc</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Rate of surplus value of high-skilled employee</t>
+          <t>Gross output (USD)</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>surplus_value.empe_hs.r.pc</t>
+          <t>gross_output.s.us</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Rate of surplus value of medium-skilled employee</t>
+          <t>Gross output (magnitude of value)</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>surplus_value.empe_ms.r.pc</t>
+          <t>gross_output.s.mv</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Rate of surplus value of low-skilled employee</t>
+          <t>Gross output (direct prices - USD)</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>surplus_value.empe_ls.r.pc</t>
+          <t>gross_output.s.du</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Complex labour multiplier</t>
+          <t>Gross Domestic Product (magnitude of value)</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>complex_labour_multiplier.emp.r.un</t>
+          <t>gdp.s.mv</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Complex labour multiplier (employee only)</t>
+          <t>Gross Domestic Product (direct prices - USD)</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>complex_labour_multiplier.empe.r.un</t>
+          <t>gdp.s.du</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Gross Domestic Product (magnitude of value)</t>
+          <t>Gross Domestic Product (USD)</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>gdp.s.mv</t>
+          <t>gdp.s.us</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Gross Domestic Product (direct prices - USD)</t>
+          <t>Value per output</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>gdp.s.du</t>
+          <t>value.m.mv</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Gross Domestic Product (USD)</t>
+          <t>Exchange rate (USD)</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>gdp.s.us</t>
+          <t>exchange.r.us</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Value per output</t>
+          <t>Complex labour multiplier</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>value.m.mv</t>
+          <t>complex_labour_multiplier.emp.r.un</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>NaN</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>Complex labour multiplier (employee only)</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>complex_labour_multiplier.empe.r.un</t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>NaN</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>Working day of employee per year (magnitude of value)</t>
+        </is>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>abstract_labour.empe.m.mv</t>
+        </is>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>Magnitude of value "created" by employee in each year. Includes productive and unproductive workers.</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>Working day of persons engaged per year (magnitude of value)</t>
+        </is>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>abstract_labour.emp.m.mv</t>
+        </is>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>Magnitude of value created by persons engaged in each year. Includes productive and unproductive workers.</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>Total exports (USD)</t>
+        </is>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>exports.s.us</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>Total exports (magnitude of value)</t>
+        </is>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>exports.s.mv</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>Total imports (USD)</t>
+        </is>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>imports.s.us</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>Total imports (magnitude of value)</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>imports.s.mv</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>Trade balance (USD)</t>
+        </is>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>trade_balance.s.us</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>Trade balance (magnitude of value)</t>
+        </is>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>trade_balance.s.mv</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>Value transfer through trade</t>
+        </is>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>trade_transfers.s.mv</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>Value transfer through trade of productive sectors</t>
+        </is>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>trade_transfers.p.s.mv</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>Value transfer through trade of unproductive sectors</t>
+        </is>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>trade_transfers.u.s.mv</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>Total real wage (constant USD)</t>
+        </is>
+      </c>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>compensation.emp.s.cu</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>Total real compensation of labour (constant USD)</t>
+        </is>
+      </c>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>compensation.empe.s.cu</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>Gross Domestic Product of productive sectors (USD)</t>
+        </is>
+      </c>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>gdp.p.s.us</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>Total profit (USD)</t>
+        </is>
+      </c>
+      <c r="B48" t="inlineStr">
+        <is>
+          <t>profit.s.us</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
+          <t>Rate of profit</t>
+        </is>
+      </c>
+      <c r="B49" t="inlineStr">
+        <is>
+          <t>appropriated_profit.r.pc</t>
+        </is>
+      </c>
+      <c r="C49" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
@@ -3124,6 +5069,11 @@
       </c>
     </row>
     <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>Standard v0.9</t>
+        </is>
+      </c>
       <c r="B2" t="inlineStr">
         <is>
           <t>WIOD16</t>
